--- a/Dataset/3_label/OPENING-CLOSING_OPENING-CLOSING_V1_0.5 divisions_per_second.xlsx
+++ b/Dataset/3_label/OPENING-CLOSING_OPENING-CLOSING_V1_0.5 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D326"/>
+  <dimension ref="A1:D332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6300,6 +6300,114 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V1_0.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>67000</v>
+      </c>
+      <c r="C327" t="n">
+        <v>40</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V1_0.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>67200</v>
+      </c>
+      <c r="C328" t="n">
+        <v>40</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V1_0.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>67400</v>
+      </c>
+      <c r="C329" t="n">
+        <v>40</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V1_0.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>67600</v>
+      </c>
+      <c r="C330" t="n">
+        <v>40</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V1_0.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>67800</v>
+      </c>
+      <c r="C331" t="n">
+        <v>40</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V1_0.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>68000</v>
+      </c>
+      <c r="C332" t="n">
+        <v>40</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
